--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80706</v>
+        <v>80708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80708</v>
+        <v>80709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>97337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97337</v>
+        <v>97345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1117,6 +1117,818 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129518805</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skog 3, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>343395</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129518818</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96320</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skog 12, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>343357</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6431972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Liten kudde.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129518832</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97801</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skog 8, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>343247</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6432016</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129518806</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skog 3, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>343395</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129518804</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>343386</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432003</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129518801</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>343350</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432013</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129518807</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skog 4, S om sumpskog, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>343357</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432032</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1351,57 +1351,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129518832</v>
+        <v>129518806</v>
       </c>
       <c r="B8" t="n">
-        <v>97801</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220686</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog 8, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 3, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>343247</v>
+        <v>343395</v>
       </c>
       <c r="R8" t="n">
-        <v>6432016</v>
+        <v>6432109</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,22 +1424,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,7 +1448,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1471,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518806</v>
+        <v>129518801</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1510,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 3, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343395</v>
+        <v>343350</v>
       </c>
       <c r="R9" t="n">
-        <v>6432109</v>
+        <v>6432013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129518801</v>
+        <v>129518807</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1740,14 +1735,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 4, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>343350</v>
+        <v>343357</v>
       </c>
       <c r="R11" t="n">
-        <v>6432013</v>
+        <v>6432032</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,53 +1811,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129518807</v>
+        <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>97801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog 4, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 8, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>343357</v>
+        <v>343247</v>
       </c>
       <c r="R12" t="n">
-        <v>6432032</v>
+        <v>6432016</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,22 +1888,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,6 +1912,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97345</v>
+        <v>97348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R9" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R10" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97801</v>
+        <v>97804</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R9" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R10" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R9" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R10" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80709</v>
+        <v>80735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97348</v>
+        <v>97377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129413392</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129413414</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129518805</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129518806</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129518801</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>129518804</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>129518807</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97804</v>
+        <v>97833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80735</v>
+        <v>80740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129413392</v>
       </c>
       <c r="B4" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129413414</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129518805</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129518806</v>
       </c>
       <c r="B8" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B9" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R9" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B10" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R10" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,7 +1699,7 @@
         <v>129518807</v>
       </c>
       <c r="B11" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97833</v>
+        <v>97845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80740</v>
+        <v>80741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129413392</v>
       </c>
       <c r="B4" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129413414</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129518805</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129518806</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129518804</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>129518801</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>129518807</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97845</v>
+        <v>97846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129413343</v>
       </c>
       <c r="B2" t="n">
-        <v>80741</v>
+        <v>80746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B9" t="n">
         <v>57896</v>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R9" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B10" t="n">
         <v>57896</v>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R10" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129518801</v>
+        <v>129518804</v>
       </c>
       <c r="B9" t="n">
         <v>57896</v>
@@ -1505,14 +1505,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343350</v>
+        <v>343386</v>
       </c>
       <c r="R9" t="n">
-        <v>6432013</v>
+        <v>6432003</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129518804</v>
+        <v>129518801</v>
       </c>
       <c r="B10" t="n">
         <v>57896</v>
@@ -1620,14 +1620,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog 2, S om sumpskog, Drängedalen, Vg</t>
+          <t>Skog 1, S om sumpskog, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343386</v>
+        <v>343350</v>
       </c>
       <c r="R10" t="n">
-        <v>6432003</v>
+        <v>6432013</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97851</v>
+        <v>97855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129413312</v>
       </c>
       <c r="B3" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97855</v>
+        <v>97857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>129518818</v>
       </c>
       <c r="B7" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97857</v>
+        <v>97867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46084-2025 artfynd.xlsx
+++ b/artfynd/A 46084-2025 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>129518832</v>
       </c>
       <c r="B12" t="n">
-        <v>97867</v>
+        <v>97871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
